--- a/data/processed/jfk_monthly_risk_summary.xlsx
+++ b/data/processed/jfk_monthly_risk_summary.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,36 +417,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>delayed_arrivals_15_plus</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>cancelled_arrivals</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_arrival_flights</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_arrival_delay_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>delay_rate</t>
         </is>
@@ -450,241 +469,2233 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>1706</v>
-      </c>
       <c r="C2" t="n">
-        <v>177</v>
+        <v>1403</v>
       </c>
       <c r="D2" t="n">
-        <v>9598</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>133575</v>
+        <v>10302</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1777453636174203</v>
+        <v>102527</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1361871481265774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>1835</v>
-      </c>
       <c r="C3" t="n">
-        <v>207</v>
+        <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>9099</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>148526</v>
+        <v>9764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2016705132432135</v>
+        <v>77578</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1191110200737403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>2148</v>
-      </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>729</v>
       </c>
       <c r="D4" t="n">
-        <v>10355</v>
+        <v>1900</v>
       </c>
       <c r="E4" t="n">
-        <v>183519</v>
+        <v>10826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.207436021245775</v>
+        <v>49261</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>43891</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06733789026417883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>1836</v>
-      </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>10269</v>
+        <v>1178</v>
       </c>
       <c r="E5" t="n">
-        <v>129108</v>
+        <v>2548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1787905346187555</v>
+        <v>3266</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>43922</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02237048665620094</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>2865</v>
-      </c>
       <c r="C6" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>10916</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
-        <v>227197</v>
+        <v>991</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2624587761084646</v>
+        <v>3113</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>43952</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05146316851664985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>3167</v>
-      </c>
       <c r="C7" t="n">
-        <v>374</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n">
-        <v>10702</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>282120</v>
+        <v>1887</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2959259951410951</v>
+        <v>6060</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05458399576046635</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>3228</v>
-      </c>
       <c r="C8" t="n">
-        <v>874</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>11182</v>
+        <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>318843</v>
+        <v>3343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2886782328742622</v>
+        <v>20409</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>44013</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.09123541728985941</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>2155</v>
-      </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>11032</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>187936</v>
+        <v>3440</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1953408266860044</v>
+        <v>17415</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08197674418604652</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>1486</v>
-      </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>10384</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>117328</v>
+        <v>3063</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1431047765793529</v>
+        <v>6111</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>44075</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.03819784524975514</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>1988</v>
-      </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>10746</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>173321</v>
+        <v>3523</v>
       </c>
       <c r="F11" t="n">
-        <v>0.18499906942118</v>
+        <v>16518</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.05591825149020721</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>1997</v>
-      </c>
       <c r="C12" t="n">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="D12" t="n">
-        <v>10359</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>156981</v>
+        <v>3647</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1927792257939956</v>
+        <v>18836</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>44136</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.07403345215245408</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
+        <v>594</v>
+      </c>
+      <c r="D13" t="n">
+        <v>97</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3704</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38443</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1603671706263499</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>422</v>
+      </c>
+      <c r="D14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3262</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28428</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1293684855916616</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>463</v>
+      </c>
+      <c r="D15" t="n">
+        <v>221</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3282</v>
+      </c>
+      <c r="F15" t="n">
+        <v>46974</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>44228</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1410725167580743</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>361</v>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4578</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23649</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.07885539536915684</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>605</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F17" t="n">
+        <v>50695</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1130841121495327</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>808</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6664</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58305</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1212484993997599</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1862</v>
+      </c>
+      <c r="D19" t="n">
+        <v>63</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7629</v>
+      </c>
+      <c r="F19" t="n">
+        <v>153069</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2440686852798532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2382</v>
+      </c>
+      <c r="D20" t="n">
+        <v>164</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8235</v>
+      </c>
+      <c r="F20" t="n">
+        <v>230005</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>44378</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2892531876138433</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D21" t="n">
+        <v>105</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8105</v>
+      </c>
+      <c r="F21" t="n">
+        <v>151832</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>44409</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2399753238741518</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1338</v>
+      </c>
+      <c r="D22" t="n">
+        <v>155</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7541</v>
+      </c>
+      <c r="F22" t="n">
+        <v>119934</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1774300490651107</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1113</v>
+      </c>
+      <c r="D23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7830</v>
+      </c>
+      <c r="F23" t="n">
+        <v>78111</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1421455938697318</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1797</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10127</v>
+      </c>
+      <c r="F24" t="n">
+        <v>107632</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>44501</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1774464303347487</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D25" t="n">
+        <v>219</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10052</v>
+      </c>
+      <c r="F25" t="n">
+        <v>148494</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2079188221249502</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2277</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11088</v>
+      </c>
+      <c r="F26" t="n">
+        <v>174876</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2053571428571428</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2436</v>
+      </c>
+      <c r="D27" t="n">
+        <v>334</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10289</v>
+      </c>
+      <c r="F27" t="n">
+        <v>189314</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.236757702400622</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2604</v>
+      </c>
+      <c r="D28" t="n">
+        <v>166</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11395</v>
+      </c>
+      <c r="F28" t="n">
+        <v>191596</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2285212812637122</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2577</v>
+      </c>
+      <c r="D29" t="n">
+        <v>529</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11188</v>
+      </c>
+      <c r="F29" t="n">
+        <v>221671</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2303360743653915</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2961</v>
+      </c>
+      <c r="D30" t="n">
+        <v>502</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11780</v>
+      </c>
+      <c r="F30" t="n">
+        <v>226902</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.251358234295416</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3158</v>
+      </c>
+      <c r="D31" t="n">
+        <v>741</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11471</v>
+      </c>
+      <c r="F31" t="n">
+        <v>299971</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2753029378432569</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3051</v>
+      </c>
+      <c r="D32" t="n">
+        <v>433</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11899</v>
+      </c>
+      <c r="F32" t="n">
+        <v>246635</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2564081015211362</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3147</v>
+      </c>
+      <c r="D33" t="n">
+        <v>473</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11834</v>
+      </c>
+      <c r="F33" t="n">
+        <v>238330</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.265928680074362</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2467</v>
+      </c>
+      <c r="D34" t="n">
+        <v>223</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11556</v>
+      </c>
+      <c r="F34" t="n">
+        <v>177079</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.2134821737625476</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2730</v>
+      </c>
+      <c r="D35" t="n">
+        <v>101</v>
+      </c>
+      <c r="E35" t="n">
+        <v>11764</v>
+      </c>
+      <c r="F35" t="n">
+        <v>165413</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2320639238354301</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2456</v>
+      </c>
+      <c r="D36" t="n">
+        <v>92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11323</v>
+      </c>
+      <c r="F36" t="n">
+        <v>170443</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2169036474432571</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3268</v>
+      </c>
+      <c r="D37" t="n">
+        <v>310</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10967</v>
+      </c>
+      <c r="F37" t="n">
+        <v>239449</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.297984863681955</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2842</v>
+      </c>
+      <c r="D38" t="n">
+        <v>87</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10912</v>
+      </c>
+      <c r="F38" t="n">
+        <v>201860</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2604472140762463</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2137</v>
+      </c>
+      <c r="D39" t="n">
+        <v>148</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10570</v>
+      </c>
+      <c r="F39" t="n">
+        <v>154344</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2021759697256386</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2931</v>
+      </c>
+      <c r="D40" t="n">
+        <v>194</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12166</v>
+      </c>
+      <c r="F40" t="n">
+        <v>218359</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2409173105375637</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3196</v>
+      </c>
+      <c r="D41" t="n">
+        <v>358</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11636</v>
+      </c>
+      <c r="F41" t="n">
+        <v>271020</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2746648332760399</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2191</v>
+      </c>
+      <c r="D42" t="n">
+        <v>67</v>
+      </c>
+      <c r="E42" t="n">
+        <v>11825</v>
+      </c>
+      <c r="F42" t="n">
+        <v>145616</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1852854122621564</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3144</v>
+      </c>
+      <c r="D43" t="n">
+        <v>528</v>
+      </c>
+      <c r="E43" t="n">
+        <v>11021</v>
+      </c>
+      <c r="F43" t="n">
+        <v>293696</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2852735686416841</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3657</v>
+      </c>
+      <c r="D44" t="n">
+        <v>929</v>
+      </c>
+      <c r="E44" t="n">
+        <v>11187</v>
+      </c>
+      <c r="F44" t="n">
+        <v>395899</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.3268972914990614</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2580</v>
+      </c>
+      <c r="D45" t="n">
+        <v>205</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11130</v>
+      </c>
+      <c r="F45" t="n">
+        <v>232328</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2318059299191375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2717</v>
+      </c>
+      <c r="D46" t="n">
+        <v>571</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10761</v>
+      </c>
+      <c r="F46" t="n">
+        <v>281747</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2524858284546046</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1789</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10913</v>
+      </c>
+      <c r="F47" t="n">
+        <v>133450</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1639329240355539</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1528</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10522</v>
+      </c>
+      <c r="F48" t="n">
+        <v>102325</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1452195400114047</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D49" t="n">
+        <v>54</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10412</v>
+      </c>
+      <c r="F49" t="n">
+        <v>148091</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1959277756434883</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2064</v>
+      </c>
+      <c r="D50" t="n">
+        <v>288</v>
+      </c>
+      <c r="E50" t="n">
+        <v>9467</v>
+      </c>
+      <c r="F50" t="n">
+        <v>179577</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2180204922361889</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1571</v>
+      </c>
+      <c r="D51" t="n">
+        <v>127</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9249</v>
+      </c>
+      <c r="F51" t="n">
+        <v>119376</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1698562006703427</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2263</v>
+      </c>
+      <c r="D52" t="n">
+        <v>80</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10162</v>
+      </c>
+      <c r="F52" t="n">
+        <v>194075</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.2226923833890966</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D53" t="n">
+        <v>109</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10153</v>
+      </c>
+      <c r="F53" t="n">
+        <v>163261</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1945237860730819</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D54" t="n">
+        <v>96</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10623</v>
+      </c>
+      <c r="F54" t="n">
+        <v>200042</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2263955568106938</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2681</v>
+      </c>
+      <c r="D55" t="n">
+        <v>360</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10459</v>
+      </c>
+      <c r="F55" t="n">
+        <v>245750</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2563342575772062</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3173</v>
+      </c>
+      <c r="D56" t="n">
+        <v>437</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10867</v>
+      </c>
+      <c r="F56" t="n">
+        <v>301579</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2919849084383915</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2899</v>
+      </c>
+      <c r="D57" t="n">
+        <v>700</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10856</v>
+      </c>
+      <c r="F57" t="n">
+        <v>275941</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2670412675018423</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1496</v>
+      </c>
+      <c r="D58" t="n">
+        <v>29</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10360</v>
+      </c>
+      <c r="F58" t="n">
+        <v>111322</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1444015444015444</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1322</v>
+      </c>
+      <c r="D59" t="n">
+        <v>72</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10726</v>
+      </c>
+      <c r="F59" t="n">
+        <v>82774</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1232519112437069</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B60" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10141</v>
+      </c>
+      <c r="F60" t="n">
+        <v>74735</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1182329158860073</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B61" t="n">
+        <v>12</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D61" t="n">
+        <v>52</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10271</v>
+      </c>
+      <c r="F61" t="n">
+        <v>192455</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.2464219647551358</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1706</v>
+      </c>
+      <c r="D62" t="n">
+        <v>177</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9598</v>
+      </c>
+      <c r="F62" t="n">
+        <v>133575</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1777453636174203</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D63" t="n">
+        <v>207</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9099</v>
+      </c>
+      <c r="F63" t="n">
+        <v>148526</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.2016705132432135</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2148</v>
+      </c>
+      <c r="D64" t="n">
+        <v>96</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10355</v>
+      </c>
+      <c r="F64" t="n">
+        <v>183519</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.207436021245775</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D65" t="n">
+        <v>51</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10269</v>
+      </c>
+      <c r="F65" t="n">
+        <v>129108</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1787905346187555</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2865</v>
+      </c>
+      <c r="D66" t="n">
+        <v>124</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10916</v>
+      </c>
+      <c r="F66" t="n">
+        <v>227197</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2624587761084646</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3167</v>
+      </c>
+      <c r="D67" t="n">
+        <v>374</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10702</v>
+      </c>
+      <c r="F67" t="n">
+        <v>282120</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2959259951410951</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3228</v>
+      </c>
+      <c r="D68" t="n">
+        <v>874</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11182</v>
+      </c>
+      <c r="F68" t="n">
+        <v>318843</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.2886782328742622</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2155</v>
+      </c>
+      <c r="D69" t="n">
+        <v>120</v>
+      </c>
+      <c r="E69" t="n">
+        <v>11032</v>
+      </c>
+      <c r="F69" t="n">
+        <v>187936</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1953408266860044</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1486</v>
+      </c>
+      <c r="D70" t="n">
+        <v>83</v>
+      </c>
+      <c r="E70" t="n">
+        <v>10384</v>
+      </c>
+      <c r="F70" t="n">
+        <v>117328</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1431047765793529</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D71" t="n">
+        <v>165</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10746</v>
+      </c>
+      <c r="F71" t="n">
+        <v>173321</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.18499906942118</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B72" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D72" t="n">
+        <v>301</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10359</v>
+      </c>
+      <c r="F72" t="n">
+        <v>156981</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.1927792257939956</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B73" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" t="n">
         <v>2916</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D73" t="n">
         <v>431</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E73" t="n">
         <v>10393</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F73" t="n">
         <v>249418</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I73" t="n">
         <v>0.2805734629077263</v>
       </c>
     </row>
